--- a/conference_registration_forms/031_rise_youth_convention_2019--conference_registration_forms.xlsx
+++ b/conference_registration_forms/031_rise_youth_convention_2019--conference_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'full_conference',_'value':_'full_conference'}</t>
+          <t>full_conference</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Full Conference', 'value': 'full_conference'}</t>
+          <t>Full Conference</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'saturday_only',_'value':_'saturday_only'}</t>
+          <t>saturday_only</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Saturday only', 'value': 'saturday_only'}</t>
+          <t>Saturday only</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_30,_'value':_30}</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 30, 'value': 30}</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_60,_'value':_60}</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 60, 'value': 60}</t>
+          <t>60</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'small',_'value':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Small', 'value': 'small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Medium', 'value': 'medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'large',_'value':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Large', 'value': 'large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_i_grant_permission',_'value':_'yes_grant'}</t>
+          <t>yes,_i_grant_permission</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, I grant permission', 'value': 'yes_grant'}</t>
+          <t>Yes, I grant permission</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'no,_i_do_not_grant_permission',_'value':_'no_deny'}</t>
+          <t>no,_i_do_not_grant_permission</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'No, I do not grant permission', 'value': 'no_deny'}</t>
+          <t>No, I do not grant permission</t>
         </is>
       </c>
     </row>
